--- a/SALT/FUNaK_AIMD.xlsx
+++ b/SALT/FUNaK_AIMD.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/SALT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/SALT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{401D9D33-C791-3048-92C7-BC532391AC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966E4E9D-C8F7-B64B-8983-3AADCA6C6A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2000" yWindow="2220" windowWidth="27640" windowHeight="16940" xr2:uid="{508FF463-2D01-1741-9B5B-BF51988EC3F1}"/>
+    <workbookView xWindow="22800" yWindow="8540" windowWidth="27640" windowHeight="16940" xr2:uid="{508FF463-2D01-1741-9B5B-BF51988EC3F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="29">
   <si>
     <t>FUNaK</t>
   </si>
@@ -138,7 +138,16 @@
     <t>expts only at ~ 36/18/4/44</t>
   </si>
   <si>
-    <t>sum</t>
+    <t>36-16-4-44</t>
+  </si>
+  <si>
+    <t>plus/minus</t>
+  </si>
+  <si>
+    <t>50-25-25</t>
+  </si>
+  <si>
+    <t>15000ps, averaging over last 2ps</t>
   </si>
 </sst>
 </file>
@@ -513,7 +522,367 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="0.0000E+00" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$67:$D$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1400</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$L$67:$L$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.7550906516787195</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.60718784384862</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4358791282584895</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8F7E-6A4C-8B53-B36AE33062BD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1576185296"/>
+        <c:axId val="1576201296"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1576185296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="900"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1576201296"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1576201296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1576185296"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1069,20 +1438,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>869950</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>679450</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>387350</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1102,6 +1987,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{149A6F2D-6602-474B-B8BD-8C3FEBCA7738}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1427,7 +2350,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D34E52-A353-6A40-833A-8122F7523B3A}">
-  <dimension ref="B3:M65"/>
+  <dimension ref="B2:M103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -1435,6 +2358,11 @@
     <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>28</v>
+      </c>
+    </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>0</v>
@@ -2404,70 +3332,677 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B60">
-        <f>D60/SUM(D60:D63)</f>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E66" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" t="s">
+        <v>6</v>
+      </c>
+      <c r="H66" t="s">
+        <v>7</v>
+      </c>
+      <c r="I66" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" t="s">
+        <v>9</v>
+      </c>
+      <c r="L66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67">
+        <v>1000</v>
+      </c>
+      <c r="E67">
+        <v>-141157.172682</v>
+      </c>
+      <c r="F67">
+        <v>22.069399000000001</v>
+      </c>
+      <c r="G67">
+        <v>998.45782399999996</v>
+      </c>
+      <c r="H67">
+        <v>-25.111764999999998</v>
+      </c>
+      <c r="I67">
+        <v>3330.4469290000002</v>
+      </c>
+      <c r="K67">
+        <f>E67+F67</f>
+        <v>-141135.103283</v>
+      </c>
+      <c r="L67">
+        <f>($H$79*(1.66E-24)/(I67*1E-24))</f>
+        <v>2.7550906516787195</v>
+      </c>
+      <c r="M67" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E68">
+        <v>1.371667</v>
+      </c>
+      <c r="F68">
+        <v>1.376177</v>
+      </c>
+      <c r="G68">
+        <v>62.260638999999998</v>
+      </c>
+      <c r="H68">
+        <v>522.68107299999997</v>
+      </c>
+      <c r="I68">
+        <v>76.299685999999994</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D69">
+        <v>1200</v>
+      </c>
+      <c r="E69">
+        <v>-141151.34962299999</v>
+      </c>
+      <c r="F69">
+        <v>26.354557</v>
+      </c>
+      <c r="G69">
+        <v>1192.325789</v>
+      </c>
+      <c r="H69">
+        <v>-31.510287999999999</v>
+      </c>
+      <c r="I69">
+        <v>3519.3794039999998</v>
+      </c>
+      <c r="K69">
+        <f>E69+F69</f>
+        <v>-141124.99506599997</v>
+      </c>
+      <c r="L69">
+        <f>($H$79*(1.66E-24)/(I69*1E-24))</f>
+        <v>2.60718784384862</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E70">
+        <v>2.1367660000000002</v>
+      </c>
+      <c r="F70">
+        <v>1.5799589999999999</v>
+      </c>
+      <c r="G70">
+        <v>71.480069999999998</v>
+      </c>
+      <c r="H70">
+        <v>581.02007600000002</v>
+      </c>
+      <c r="I70">
+        <v>135.36157800000001</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D71">
+        <v>1400</v>
+      </c>
+      <c r="E71">
+        <v>-141143.59498699999</v>
+      </c>
+      <c r="F71">
+        <v>30.773126999999999</v>
+      </c>
+      <c r="G71">
+        <v>1392.2295429999999</v>
+      </c>
+      <c r="H71">
+        <v>-7.3851699999999996</v>
+      </c>
+      <c r="I71">
+        <v>3766.8877299999999</v>
+      </c>
+      <c r="K71">
+        <f>E71+F71</f>
+        <v>-141112.82186</v>
+      </c>
+      <c r="L71">
+        <f>($H$79*(1.66E-24)/(I71*1E-24))</f>
+        <v>2.4358791282584895</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E72">
+        <v>2.183942</v>
+      </c>
+      <c r="F72">
+        <v>1.9108940000000001</v>
+      </c>
+      <c r="G72">
+        <v>86.452156000000002</v>
+      </c>
+      <c r="H72">
+        <v>601.82682699999998</v>
+      </c>
+      <c r="I72">
+        <v>128.87987000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D74">
+        <f>F74/SUM(F74:F77)</f>
         <v>0.36</v>
       </c>
-      <c r="C60" t="s">
+      <c r="E74" t="s">
         <v>11</v>
       </c>
-      <c r="D60">
+      <c r="F74">
         <v>18</v>
       </c>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B61">
-        <f>D61/SUM(D60:D63)</f>
+      <c r="G74">
+        <v>22.99</v>
+      </c>
+      <c r="H74">
+        <f>F74*G74</f>
+        <v>413.82</v>
+      </c>
+      <c r="J74">
+        <v>1000</v>
+      </c>
+      <c r="K74">
+        <v>-141135.103283</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D75">
+        <f>F75/SUM(F74:F77)</f>
         <v>0.16</v>
       </c>
-      <c r="C61" t="s">
+      <c r="E75" t="s">
         <v>12</v>
       </c>
-      <c r="D61">
+      <c r="F75">
         <v>8</v>
       </c>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B62">
-        <f>D62/SUM(D60:D63)</f>
+      <c r="G75">
+        <v>39.1</v>
+      </c>
+      <c r="H75">
+        <f t="shared" ref="H75:H78" si="5">F75*G75</f>
+        <v>312.8</v>
+      </c>
+      <c r="J75">
+        <v>1200</v>
+      </c>
+      <c r="K75">
+        <v>-141124.99506599997</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D76">
+        <f>F76/SUM(F74:F77)</f>
         <v>0.04</v>
       </c>
-      <c r="C62" t="s">
+      <c r="E76" t="s">
         <v>13</v>
       </c>
-      <c r="D62">
+      <c r="F76">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B63">
-        <f>D63/SUM(D60:D63)</f>
+      <c r="G76">
+        <v>238.03</v>
+      </c>
+      <c r="H76">
+        <f>F76*G76</f>
+        <v>476.06</v>
+      </c>
+      <c r="J76">
+        <v>1400</v>
+      </c>
+      <c r="K76">
+        <v>-141112.82186</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="D77">
+        <f>F77/SUM(F74:F77)</f>
         <v>0.44</v>
       </c>
-      <c r="C63" t="s">
+      <c r="E77" t="s">
         <v>14</v>
       </c>
-      <c r="D63">
+      <c r="F77">
         <v>22</v>
       </c>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="C64" t="s">
+      <c r="G77">
+        <v>91.22</v>
+      </c>
+      <c r="H77">
+        <f t="shared" ref="H77:H80" si="6">F77*G77</f>
+        <v>2006.84</v>
+      </c>
+    </row>
+    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="E78" t="s">
         <v>15</v>
       </c>
-      <c r="D64">
-        <f>D60+D61+4*D62+4*D63</f>
+      <c r="F78">
         <v>122</v>
       </c>
-    </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C65" t="s">
+      <c r="G78">
+        <v>19</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="6"/>
+        <v>2318</v>
+      </c>
+      <c r="K78" cm="1">
+        <f t="array" ref="K78:L78">LINEST(K74:K76,J74:J76)</f>
+        <v>5.5703557500019089E-2</v>
+      </c>
+      <c r="L78">
+        <v>-141191.15100533335</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="F79">
+        <f>SUM(F74:F78)</f>
+        <v>172</v>
+      </c>
+      <c r="H79">
+        <f>SUM(H74:H78)</f>
+        <v>5527.52</v>
+      </c>
+      <c r="I79" t="s">
+        <v>16</v>
+      </c>
+      <c r="K79">
+        <f>K78/SUM(F74:F77)*(1.6E-19)*(6.022E+23)</f>
+        <v>107.34298344483678</v>
+      </c>
+      <c r="L79" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="H80">
+        <f>H79*1.66E-24</f>
+        <v>9.1756832000000005E-21</v>
+      </c>
+      <c r="I80" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K81" t="s">
+        <v>20</v>
+      </c>
+      <c r="L81" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K82">
+        <v>115</v>
+      </c>
+      <c r="L82">
         <v>25</v>
       </c>
-      <c r="D65">
-        <f>SUM(D60:D64)</f>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K83">
+        <v>117</v>
+      </c>
+      <c r="L83">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B85" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="E86" t="s">
+        <v>4</v>
+      </c>
+      <c r="F86" t="s">
+        <v>5</v>
+      </c>
+      <c r="G86" t="s">
+        <v>6</v>
+      </c>
+      <c r="H86" t="s">
+        <v>7</v>
+      </c>
+      <c r="I86" t="s">
+        <v>8</v>
+      </c>
+      <c r="K86" t="s">
+        <v>9</v>
+      </c>
+      <c r="L86" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B87" t="s">
+        <v>27</v>
+      </c>
+      <c r="D87">
+        <v>1000</v>
+      </c>
+      <c r="E87">
+        <v>-141157.172682</v>
+      </c>
+      <c r="F87">
+        <v>22.069399000000001</v>
+      </c>
+      <c r="G87">
+        <v>998.45782399999996</v>
+      </c>
+      <c r="H87">
+        <v>-25.111764999999998</v>
+      </c>
+      <c r="I87">
+        <v>3330.4469290000002</v>
+      </c>
+      <c r="K87">
+        <f>E87+F87</f>
+        <v>-141135.103283</v>
+      </c>
+      <c r="L87">
+        <f>($H$79*(1.66E-24)/(I87*1E-24))</f>
+        <v>2.7550906516787195</v>
+      </c>
+    </row>
+    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="E88">
+        <v>1.371667</v>
+      </c>
+      <c r="F88">
+        <v>1.376177</v>
+      </c>
+      <c r="G88">
+        <v>62.260638999999998</v>
+      </c>
+      <c r="H88">
+        <v>522.68107299999997</v>
+      </c>
+      <c r="I88">
+        <v>76.299685999999994</v>
+      </c>
+    </row>
+    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D89">
+        <v>1200</v>
+      </c>
+      <c r="E89">
+        <v>-141151.34962299999</v>
+      </c>
+      <c r="F89">
+        <v>26.354557</v>
+      </c>
+      <c r="G89">
+        <v>1192.325789</v>
+      </c>
+      <c r="H89">
+        <v>-31.510287999999999</v>
+      </c>
+      <c r="I89">
+        <v>3519.3794039999998</v>
+      </c>
+      <c r="K89">
+        <f>E89+F89</f>
+        <v>-141124.99506599997</v>
+      </c>
+      <c r="L89">
+        <f>($H$79*(1.66E-24)/(I89*1E-24))</f>
+        <v>2.60718784384862</v>
+      </c>
+    </row>
+    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="E90">
+        <v>2.1367660000000002</v>
+      </c>
+      <c r="F90">
+        <v>1.5799589999999999</v>
+      </c>
+      <c r="G90">
+        <v>71.480069999999998</v>
+      </c>
+      <c r="H90">
+        <v>581.02007600000002</v>
+      </c>
+      <c r="I90">
+        <v>135.36157800000001</v>
+      </c>
+    </row>
+    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D91">
+        <v>1400</v>
+      </c>
+      <c r="E91">
+        <v>-141143.59498699999</v>
+      </c>
+      <c r="F91">
+        <v>30.773126999999999</v>
+      </c>
+      <c r="G91">
+        <v>1392.2295429999999</v>
+      </c>
+      <c r="H91">
+        <v>-7.3851699999999996</v>
+      </c>
+      <c r="I91">
+        <v>3766.8877299999999</v>
+      </c>
+      <c r="K91">
+        <f>E91+F91</f>
+        <v>-141112.82186</v>
+      </c>
+      <c r="L91">
+        <f>($H$79*(1.66E-24)/(I91*1E-24))</f>
+        <v>2.4358791282584895</v>
+      </c>
+    </row>
+    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="E92">
+        <v>2.183942</v>
+      </c>
+      <c r="F92">
+        <v>1.9108940000000001</v>
+      </c>
+      <c r="G92">
+        <v>86.452156000000002</v>
+      </c>
+      <c r="H92">
+        <v>601.82682699999998</v>
+      </c>
+      <c r="I92">
+        <v>128.87987000000001</v>
+      </c>
+    </row>
+    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D94">
+        <f>F94/SUM(F94:F97)</f>
+        <v>0.36</v>
+      </c>
+      <c r="E94" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94">
+        <v>18</v>
+      </c>
+      <c r="G94">
+        <v>22.99</v>
+      </c>
+      <c r="H94">
+        <f>F94*G94</f>
+        <v>413.82</v>
+      </c>
+      <c r="J94">
+        <v>1000</v>
+      </c>
+      <c r="K94">
+        <v>-141135.103283</v>
+      </c>
+    </row>
+    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D95">
+        <f>F95/SUM(F94:F97)</f>
+        <v>0.16</v>
+      </c>
+      <c r="E95" t="s">
+        <v>12</v>
+      </c>
+      <c r="F95">
+        <v>8</v>
+      </c>
+      <c r="G95">
+        <v>39.1</v>
+      </c>
+      <c r="H95">
+        <f t="shared" ref="H95:H98" si="7">F95*G95</f>
+        <v>312.8</v>
+      </c>
+      <c r="J95">
+        <v>1200</v>
+      </c>
+      <c r="K95">
+        <v>-141124.99506599997</v>
+      </c>
+    </row>
+    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D96">
+        <f>F96/SUM(F94:F97)</f>
+        <v>0.04</v>
+      </c>
+      <c r="E96" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96">
+        <v>2</v>
+      </c>
+      <c r="G96">
+        <v>238.03</v>
+      </c>
+      <c r="H96">
+        <f>F96*G96</f>
+        <v>476.06</v>
+      </c>
+      <c r="J96">
+        <v>1400</v>
+      </c>
+      <c r="K96">
+        <v>-141112.82186</v>
+      </c>
+    </row>
+    <row r="97" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="D97">
+        <f>F97/SUM(F94:F97)</f>
+        <v>0.44</v>
+      </c>
+      <c r="E97" t="s">
+        <v>14</v>
+      </c>
+      <c r="F97">
+        <v>22</v>
+      </c>
+      <c r="G97">
+        <v>91.22</v>
+      </c>
+      <c r="H97">
+        <f t="shared" ref="H97:H100" si="8">F97*G97</f>
+        <v>2006.84</v>
+      </c>
+    </row>
+    <row r="98" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="E98" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98">
+        <v>122</v>
+      </c>
+      <c r="G98">
+        <v>19</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="8"/>
+        <v>2318</v>
+      </c>
+      <c r="K98" cm="1">
+        <f t="array" ref="K98:L98">LINEST(K94:K96,J94:J96)</f>
+        <v>5.5703557500019089E-2</v>
+      </c>
+      <c r="L98">
+        <v>-141191.15100533335</v>
+      </c>
+    </row>
+    <row r="99" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="F99">
+        <f>SUM(F94:F98)</f>
         <v>172</v>
+      </c>
+      <c r="H99">
+        <f>SUM(H94:H98)</f>
+        <v>5527.52</v>
+      </c>
+      <c r="I99" t="s">
+        <v>16</v>
+      </c>
+      <c r="K99">
+        <f>K98/SUM(F94:F97)*(1.6E-19)*(6.022E+23)</f>
+        <v>107.34298344483678</v>
+      </c>
+      <c r="L99" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="H100">
+        <f>H99*1.66E-24</f>
+        <v>9.1756832000000005E-21</v>
+      </c>
+      <c r="I100" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="101" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="K101" t="s">
+        <v>20</v>
+      </c>
+      <c r="L101" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="K102">
+        <v>115</v>
+      </c>
+      <c r="L102">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="4:12" x14ac:dyDescent="0.2">
+      <c r="K103">
+        <v>117</v>
+      </c>
+      <c r="L103">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
